--- a/real_estate_forms/007_real_estate_lead_form--real_estate_forms.xlsx
+++ b/real_estate_forms/007_real_estate_lead_form--real_estate_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -711,8 +711,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -774,12 +774,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'name':_'name',_'label':_'full_name',_'type':_'text'}</t>
+          <t>full_name</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'name': 'name', 'label': 'Full Name', 'type': 'text'}</t>
+          <t>Full Name</t>
         </is>
       </c>
     </row>
@@ -791,12 +791,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'name':_'email',_'label':_'email',_'type':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'name': 'email', 'label': 'Email', 'type': 'email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -808,12 +808,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'name':_'phone',_'label':_'phone',_'type':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'name': 'phone', 'label': 'Phone', 'type': 'phone'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -825,12 +825,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'name':_'address',_'label':_'address',_'type':_'text'}</t>
+          <t>address</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'name': 'address', 'label': 'Address', 'type': 'text'}</t>
+          <t>Address</t>
         </is>
       </c>
     </row>
@@ -842,12 +842,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'name':_'property_type',_'label':_'property_type',_'type':_'select_one',_'options':_[{'id':_1,_'name':_'house',_'value':_'house'},_{'id':_2,_'name':_'apartment',_'value':_'apartment'},_{'id':_3,_'name':_'other',_'value':_'other'}]}</t>
+          <t>property_type</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'name': 'property_type', 'label': 'Property Type', 'type': 'select_one', 'options': [{'id': 1, 'name': 'House', 'value': 'House'}, {'id': 2, 'name': 'Apartment', 'value': 'Apartment'}, {'id': 3, 'name': 'Other', 'value': 'Other'}]}</t>
+          <t>Property Type</t>
         </is>
       </c>
     </row>
@@ -859,12 +859,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'name':_'property_location',_'label':_'property_location',_'type':_'select_one',_'options':_[{'id':_1,_'name':_'location_1',_'value':_'location_1'},_{'id':_2,_'name':_'location_2',_'value':_'location_2'},_{'id':_3,_'name':_'location_3',_'value':_'location_3'}]}</t>
+          <t>property_location</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'name': 'property_location', 'label': 'Property Location', 'type': 'select_one', 'options': [{'id': 1, 'name': 'Location 1', 'value': 'Location 1'}, {'id': 2, 'name': 'Location 2', 'value': 'Location 2'}, {'id': 3, 'name': 'Location 3', 'value': 'Location 3'}]}</t>
+          <t>Property Location</t>
         </is>
       </c>
     </row>
@@ -876,12 +876,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'to_buy',_'value':_'to_buy'}</t>
+          <t>to_buy</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'To Buy', 'value': 'To Buy'}</t>
+          <t>To Buy</t>
         </is>
       </c>
     </row>
@@ -893,12 +893,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'to_rent',_'value':_'to_rent'}</t>
+          <t>to_rent</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'To Rent', 'value': 'To Rent'}</t>
+          <t>To Rent</t>
         </is>
       </c>
     </row>
@@ -910,12 +910,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Other', 'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -927,12 +927,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'month_1',_'value':_'month_1'}</t>
+          <t>month_1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Month 1', 'value': 'Month 1'}</t>
+          <t>Month 1</t>
         </is>
       </c>
     </row>
@@ -944,12 +944,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'month_2',_'value':_'month_2'}</t>
+          <t>month_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Month 2', 'value': 'Month 2'}</t>
+          <t>Month 2</t>
         </is>
       </c>
     </row>
@@ -961,12 +961,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'month_3',_'value':_'month_3'}</t>
+          <t>month_3</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Month 3', 'value': 'Month 3'}</t>
+          <t>Month 3</t>
         </is>
       </c>
     </row>
@@ -978,12 +978,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'year_1',_'value':_'year_1'}</t>
+          <t>year_1</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Year 1', 'value': 'Year 1'}</t>
+          <t>Year 1</t>
         </is>
       </c>
     </row>
@@ -995,12 +995,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'year_2',_'value':_'year_2'}</t>
+          <t>year_2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Year 2', 'value': 'Year 2'}</t>
+          <t>Year 2</t>
         </is>
       </c>
     </row>
@@ -1012,12 +1012,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'year_3',_'value':_'year_3'}</t>
+          <t>year_3</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Year 3', 'value': 'Year 3'}</t>
+          <t>Year 3</t>
         </is>
       </c>
     </row>
